--- a/文档/2.项目开发计划表（按项目小组提交）/项目开发计划表-叶世豪小组.xlsx
+++ b/文档/2.项目开发计划表（按项目小组提交）/项目开发计划表-叶世豪小组.xlsx
@@ -1478,7 +1478,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" ns1:Ignorable="x14ac">
   <sheetPr>
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
@@ -1503,29 +1503,37 @@
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>2</v>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">智能在线学习考试系统</t>
+        </is>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="3" t="s">
-        <v>4</v>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">叶世豪组</t>
+        </is>
       </c>
       <c r="F3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="5" t="s">
-        <v>6</v>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">叶世豪</t>
+        </is>
       </c>
     </row>
     <row r="4" ht="24.949999999999999" customHeight="1">
       <c r="A4" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="7" t="s">
-        <v>8</v>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10个工作日</t>
+        </is>
       </c>
       <c r="C4" s="8" t="s">
         <v>9</v>
@@ -1587,27 +1595,75 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" ht="185" customHeight="1">
-      <c r="A7" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D7" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="E7" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="F7" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G7" s="13" t="s">
-        <v>24</v>
+    <row r="7" ht="205" customHeight="1">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">工作任务：
+1. 叶世豪：召开项目启动会，确认MVP范围、提交材料、10天开发节奏和答辩要求。
+2. 贺治中：搭建学习资料管理模块开发环境，梳理图文、文档、视频和附件上传所需组件。
+3. 叶世豪：搭建在线学习与AI助手、订单与后台支付相关开发环境，确认AI模型API和支付模拟方案。
+4. 黄浩：搭建题库与考试管理模块开发环境，整理五类题型和固定组卷需求。
+5. 罗逸欢：搭建在线答题与阅卷模块开发环境，确认倒计时、自动保存、自动交卷和评分流程。</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">工作任务：
+1. 叶世豪：组织需求评审，明确普通用户、发布者、管理员三类角色的权限边界。
+2. 贺治中：完成学习资料管理模块需求细化和数据表设计，包括资料、分类、附件、审核状态等。
+3. 叶世豪：完成在线学习、AI助手、订单、权益、额度、后台管理等流程和表结构设计。
+4. 黄浩：完成题库、题目、试卷、考试发布、指定考生、考试次数扣除等表结构设计。
+5. 罗逸欢：完成答卷、答案保存、阅卷记录、成绩统计、题目正确率等表结构设计。</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">工作任务：
+1. 贺治中：开发学习资料管理模块，完成图文、文档、视频及附件的创建、编辑和上传。
+2. 贺治中：实现资料免费/付费状态、价格设置、草稿、待审核、已发布、已下架等状态流转。
+3. 叶世豪：配合完成资料访问权限校验，保证免费资料可直接学习、付费资料需购买后访问。
+4. 全体成员：完成学习资料管理模块自测，整理资料上传、审核、发布和下架的演示数据。</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">工作任务：
+1. 叶世豪：开发在线学习与AI助手模块，完成学习进度、最后学习时间、收藏、点赞和评论功能。
+2. 叶世豪：实现AI资料总结，支持生成内容摘要、核心知识点和复习提纲。
+3. 叶世豪：实现AI知识讲解，支持围绕当前资料提问并返回解释、举例和分步骤讲解。
+4. 贺治中：配合提供资料内容读取和文字提取接口，保证AI功能可基于学习资料调用。
+5. 全体成员：完成在线学习与AI助手模块联调。</t>
+        </is>
+      </c>
+      <c r="E7" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">工作任务：
+1. 黄浩：开发题库与考试管理模块，完成单选、多选、判断、填空、简答五类题型维护。
+2. 黄浩：实现题干、选项、正确答案、答案解析、分值和题型等字段校验。
+3. 黄浩：实现固定组卷、手动添加题目、试卷总分统计和试卷预览。
+4. 黄浩：实现考试发布、考试时间、答题时长、及格分数、指定考生和考试次数扣除。
+5. 罗逸欢：配合确认考试发布数据满足后续答题和阅卷流程。</t>
+        </is>
+      </c>
+      <c r="F7" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">工作任务：
+1. 罗逸欢：开发在线答题与阅卷模块，完成考试说明、开始考试、逐题作答和答题卡记录。
+2. 罗逸欢：实现答案定时保存、页面刷新恢复、提交试卷和超时自动交卷。
+3. 罗逸欢：实现客观题自动评分，支持单选、多选、判断题自动判分。
+4. 罗逸欢：实现填空题复核、简答题人工评分和最终成绩生成。
+5. 黄浩：配合校验题目答案、分值和试卷总分规则。</t>
+        </is>
+      </c>
+      <c r="G7" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">工作任务：
+1. 叶世豪：开发订单与后台支付模块，完成模拟支付、订单创建、支付成功和权益发放流程。
+2. 叶世豪：实现付费学习资料访问权限、AI次数包、考试发布次数包和额度扣除规则。
+3. 叶世豪：实现后台用户、内容、考试、订单、AI配置和操作日志管理。
+4. 贺治中、黄浩、罗逸欢：分别对接资料购买权限、AI额度、考试次数、成绩统计等模块数据。
+5. 全体成员：完成付费资料、AI次数、考试次数三类核心付费场景联调。</t>
+        </is>
       </c>
     </row>
     <row r="8" ht="20.100000000000001" customHeight="1">
@@ -1640,15 +1696,37 @@
       <c r="F9" s="12"/>
       <c r="G9" s="12"/>
     </row>
-    <row r="10" ht="185" customHeight="1">
-      <c r="A10" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="B10" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="C10" s="13" t="s">
-        <v>27</v>
+    <row r="10" ht="220" customHeight="1">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">工作任务：
+1. 贺治中：联调学习资料管理模块，检查资料创建、上传、审核、发布、下架和付费访问流程。
+2. 叶世豪：联调在线学习与AI助手、订单与后台支付模块，检查学习记录、AI扣次、权益发放和后台管理。
+3. 黄浩：联调题库与考试管理模块，检查题型维护、固定组卷、考试发布和指定考生流程。
+4. 罗逸欢：联调在线答题与阅卷模块，检查自动保存、自动交卷、自动评分、人工评分和成绩统计。
+5. 全体成员：串联普通用户、发布者、管理员三类角色完成端到端演示流程。</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">工作任务：
+1. 贺治中：修复学习资料管理模块Bug，补充资料分类、附件上传、审核状态等演示数据。
+2. 叶世豪：修复在线学习、AI助手、订单后台相关Bug，补充AI次数包和订单演示数据。
+3. 黄浩：修复题库与考试管理模块Bug，补充题库、试卷、考试发布和指定考生演示数据。
+4. 罗逸欢：修复在线答题与阅卷模块Bug，补充答卷、成绩、正确率和阅卷演示数据。
+5. 全体成员：完成系统测试记录，整理项目设计报告、开发计划表和实习报告材料。</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">工作任务：
+1. 叶世豪：统筹答辩准备，梳理项目背景、MVP目标、技术架构和整体演示流程。
+2. 贺治中：准备学习资料管理模块答辩说明，展示资料创建、上传、审核、发布和付费访问。
+3. 叶世豪：准备在线学习与AI助手、订单与后台支付模块答辩说明，展示AI总结、知识讲解、支付和权益发放。
+4. 黄浩：准备题库与考试管理模块答辩说明，展示题库维护、固定组卷、考试发布和考试次数扣除。
+5. 罗逸欢：准备在线答题与阅卷模块答辩说明，展示答案保存、自动交卷、自动评分、人工阅卷和成绩统计。
+6. 全体成员：完成最终Bug检查、PPT演练和答辩分工确认。</t>
+        </is>
       </c>
       <c r="D10" s="16"/>
       <c r="E10" s="16"/>
